--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -794,6 +794,156 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,45 +812,45 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1746</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -880,37 +880,37 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -906,39 +906,9 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>829</v>
+        <v>1018</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07 12:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-07-07 12:57</t>
         </is>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -914,6 +914,36 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 19:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,15 +812,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1746</v>
+        <v>3336</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -842,15 +842,15 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -872,15 +872,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -902,15 +902,15 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1018</v>
+        <v>2375</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1373</v>
+        <v>1157</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 19:26</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,15 +812,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3336</v>
+        <v>3603</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -842,15 +842,15 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -902,15 +902,15 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2375</v>
+        <v>2600</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1157</v>
+        <v>1435</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -794,156 +794,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Academias</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3603</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1435</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -794,6 +794,156 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2614</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,45 +812,45 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3624</v>
+        <v>4076</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -872,45 +872,45 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1928</v>
+        <v>6364</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>2614</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2808</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1442</v>
+        <v>1561</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,15 +812,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4076</v>
+        <v>4521</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -842,15 +842,15 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -872,15 +872,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6364</v>
+        <v>6793</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -902,15 +902,15 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2808</v>
+        <v>2886</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1561</v>
+        <v>1872</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -812,15 +812,15 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4521</v>
+        <v>4951</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -842,15 +842,15 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -872,15 +872,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6793</v>
+        <v>6982</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -902,15 +902,15 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2886</v>
+        <v>2966</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -932,15 +932,15 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1872</v>
+        <v>1939</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -944,6 +944,156 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5053</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7177</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2999</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,45 +962,45 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5053</v>
+        <v>6109</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>323</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>348</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1022,45 +1022,45 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7177</v>
+        <v>7609</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>2999</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>4008</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1972</v>
+        <v>2444</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,15 +962,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6109</v>
+        <v>6738</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -992,15 +992,15 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>348</v>
+        <v>485</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7609</v>
+        <v>7966</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4008</v>
+        <v>4531</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2444</v>
+        <v>2707</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,15 +962,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6738</v>
+        <v>7054</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -992,15 +992,15 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>485</v>
+        <v>577</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7966</v>
+        <v>8549</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4531</v>
+        <v>4667</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2707</v>
+        <v>2844</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,15 +962,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7054</v>
+        <v>8454</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -992,15 +992,15 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>577</v>
+        <v>622</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8549</v>
+        <v>8893</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4667</v>
+        <v>4979</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2844</v>
+        <v>3095</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,15 +962,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>8454</v>
+        <v>9091</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -992,15 +992,15 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8893</v>
+        <v>9339</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4979</v>
+        <v>5070</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3095</v>
+        <v>3204</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -962,15 +962,15 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9091</v>
+        <v>9280</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -992,15 +992,15 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>653</v>
+        <v>707</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9339</v>
+        <v>9590</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5070</v>
+        <v>5167</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3204</v>
+        <v>3252</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1094,6 +1094,156 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>9398</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>730</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5207</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3287</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,45 +1112,45 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9398</v>
+        <v>9730</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>730</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1172,45 +1172,45 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9800</v>
+        <v>10328</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>5207</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>5304</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3287</v>
+        <v>3375</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,15 +1112,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9730</v>
+        <v>10114</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10328</v>
+        <v>10707</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5304</v>
+        <v>5628</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3375</v>
+        <v>3468</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,15 +1112,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10114</v>
+        <v>10379</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10707</v>
+        <v>11352</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5628</v>
+        <v>5756</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3468</v>
+        <v>3678</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,15 +1112,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10379</v>
+        <v>10726</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11352</v>
+        <v>11947</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5756</v>
+        <v>6014</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3678</v>
+        <v>3786</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,15 +1112,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10726</v>
+        <v>10996</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>816</v>
+        <v>893</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11947</v>
+        <v>12573</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6014</v>
+        <v>6098</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3786</v>
+        <v>3921</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1112,15 +1112,15 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10996</v>
+        <v>11197</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12573</v>
+        <v>12742</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1202,15 +1202,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6098</v>
+        <v>6212</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3921</v>
+        <v>3958</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1244,6 +1244,156 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>11402</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>986</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>12926</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>6334</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>3994</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1262,45 +1262,45 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11402</v>
+        <v>11897</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>986</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1322,45 +1322,45 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>12926</v>
+        <v>13156</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>6334</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>6636</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>3994</v>
+        <v>5528</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1262,15 +1262,15 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11897</v>
+        <v>14133</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1322,15 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>13156</v>
+        <v>14416</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1352,15 +1352,15 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6636</v>
+        <v>6758</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5528</v>
+        <v>5904</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1262,15 +1262,15 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>14133</v>
+        <v>15468</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1322,15 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>14416</v>
+        <v>14778</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1352,15 +1352,15 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6758</v>
+        <v>6828</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5904</v>
+        <v>5999</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1262,15 +1262,15 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15468</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1076</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1322,15 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>14778</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1352,15 +1352,15 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6828</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>5999</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1257,20 +1257,20 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1287,20 +1287,20 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1317,20 +1317,20 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1262,15 +1262,15 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1292,15 +1292,15 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1322,15 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1352,15 +1352,15 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1394,6 +1394,156 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,45 +1412,45 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>426</v>
+        <v>1835</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1472,45 +1472,45 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>372</v>
+        <v>686</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>125</v>
+        <v>311</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,15 +1412,15 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1835</v>
+        <v>2418</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>686</v>
+        <v>906</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,15 +1412,15 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2418</v>
+        <v>2747</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>906</v>
+        <v>1119</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>214</v>
+        <v>305</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>393</v>
+        <v>586</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,15 +1412,15 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2747</v>
+        <v>3138</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1119</v>
+        <v>1539</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>586</v>
+        <v>784</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,15 +1412,15 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3138</v>
+        <v>3353</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1539</v>
+        <v>2091</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>338</v>
+        <v>411</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>784</v>
+        <v>890</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1412,15 +1412,15 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3353</v>
+        <v>3510</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1472,15 +1472,15 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2091</v>
+        <v>2368</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>890</v>
+        <v>945</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1544,6 +1544,156 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3723</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2507</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,45 +1562,45 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3723</v>
+        <v>3904</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>S33/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>371</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -1622,45 +1622,45 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2507</v>
+        <v>2702</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>S33/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>646</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>752</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1334</v>
+        <v>1800</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,15 +1562,15 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3904</v>
+        <v>4179</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1592,15 +1592,15 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2702</v>
+        <v>3052</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>752</v>
+        <v>952</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1800</v>
+        <v>2060</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,15 +1562,15 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>4179</v>
+        <v>4518</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1592,15 +1592,15 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>446</v>
+        <v>502</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3052</v>
+        <v>4274</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>952</v>
+        <v>1079</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2060</v>
+        <v>2378</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,15 +1562,15 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>4518</v>
+        <v>4727</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1592,15 +1592,15 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>502</v>
+        <v>537</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4274</v>
+        <v>5179</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1079</v>
+        <v>1217</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2378</v>
+        <v>2492</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,15 +1562,15 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>4727</v>
+        <v>4914</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1592,15 +1592,15 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5179</v>
+        <v>5568</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1217</v>
+        <v>1381</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2492</v>
+        <v>2603</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1562,15 +1562,15 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>4914</v>
+        <v>5020</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1592,15 +1592,15 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5568</v>
+        <v>5730</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1652,15 +1652,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1381</v>
+        <v>1414</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2603</v>
+        <v>2652</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1694,6 +1694,156 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>5120</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>5885</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1434</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2682</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,45 +1712,45 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5120</v>
+        <v>5387</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>649</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -1772,45 +1772,45 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>5885</v>
+        <v>6143</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>1434</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2220</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2682</v>
+        <v>2815</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,15 +1712,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5387</v>
+        <v>5482</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>679</v>
+        <v>717</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -1772,15 +1772,15 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6143</v>
+        <v>6494</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -1802,15 +1802,15 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2220</v>
+        <v>2480</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2815</v>
+        <v>2955</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,15 +1712,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5482</v>
+        <v>5582</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -1772,15 +1772,15 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6494</v>
+        <v>6906</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -1802,15 +1802,15 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2480</v>
+        <v>2613</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2955</v>
+        <v>3020</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,15 +1712,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5582</v>
+        <v>5828</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>732</v>
+        <v>782</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -1772,15 +1772,15 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6906</v>
+        <v>7418</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -1802,15 +1802,15 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2613</v>
+        <v>2767</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3020</v>
+        <v>3141</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,15 +1712,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5828</v>
+        <v>5962</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>782</v>
+        <v>828</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -1772,15 +1772,15 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>7418</v>
+        <v>7716</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -1802,15 +1802,15 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2767</v>
+        <v>2863</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3141</v>
+        <v>3296</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1712,15 +1712,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5962</v>
+        <v>6023</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -1772,15 +1772,15 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>7716</v>
+        <v>8228</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -1802,15 +1802,15 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2863</v>
+        <v>3010</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -1832,15 +1832,15 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3296</v>
+        <v>3330</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1844,6 +1844,156 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>6064</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>8427</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>3052</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>3359</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,45 +1862,45 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>6064</v>
+        <v>6248</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>866</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>886</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -1922,45 +1922,45 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>8427</v>
+        <v>9150</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>3052</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3119</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3359</v>
+        <v>3672</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>6248</v>
+        <v>6377</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>9150</v>
+        <v>10263</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3119</v>
+        <v>3198</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3672</v>
+        <v>3783</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>6377</v>
+        <v>6803</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>10263</v>
+        <v>11336</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3198</v>
+        <v>4081</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3783</v>
+        <v>3838</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>6803</v>
+        <v>7036</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>11336</v>
+        <v>12053</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4081</v>
+        <v>4163</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3838</v>
+        <v>4387</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>7036</v>
+        <v>7182</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>12053</v>
+        <v>12398</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4163</v>
+        <v>4199</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>4387</v>
+        <v>4417</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>7182</v>
+        <v>7372</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -1892,15 +1892,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>12398</v>
+        <v>12773</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -1952,15 +1952,15 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4199</v>
+        <v>4220</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>4417</v>
+        <v>4448</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1994,6 +1994,156 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2007,50 +2007,50 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2067,50 +2067,50 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2127,20 +2127,20 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2012,15 +2012,15 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>258</v>
+        <v>773</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2042,15 +2042,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>164</v>
+        <v>458</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>448</v>
+        <v>1305</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>211</v>
+        <v>552</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2132,15 +2132,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>188</v>
+        <v>509</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2012,15 +2012,15 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>773</v>
+        <v>1153</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2042,15 +2042,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1305</v>
+        <v>1617</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>552</v>
+        <v>1039</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2132,15 +2132,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>509</v>
+        <v>549</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2012,15 +2012,15 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1153</v>
+        <v>1420</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2042,15 +2042,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1617</v>
+        <v>1892</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1039</v>
+        <v>1246</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2132,15 +2132,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>549</v>
+        <v>656</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2012,15 +2012,15 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1420</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2042,15 +2042,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1892</v>
+        <v>2142</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2132,15 +2132,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>656</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2012,7 +2012,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2142</v>
+        <v>2305</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2144,6 +2144,156 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,37 +2170,37 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,37 +2230,37 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_interacoes_total.xlsx
+++ b/instagram-metrics/base_interacoes_total.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
